--- a/plots/countries/sectors/Brunei-sectors.xlsx
+++ b/plots/countries/sectors/Brunei-sectors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Author</t>
   </si>
@@ -30,13 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2025). Tidy GHG Inventories (1.0) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14945466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -443,14 +437,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -464,39 +450,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>2010</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>0.0481160872447636</v>
@@ -504,19 +490,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>2010</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0.0813386165317343</v>
@@ -524,19 +510,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>1.78071432468676</v>
@@ -544,19 +530,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>2010</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>0.353068322610491</v>
@@ -564,19 +550,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>2010</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>6.0094056337199</v>
@@ -584,19 +570,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>2010</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
         <v>1.21525842637276</v>
@@ -604,19 +590,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>2010</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>1.04225</v>
@@ -624,19 +610,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>2010</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>-4.00416979600036</v>
@@ -644,19 +630,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>2010</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>0.13993159665777</v>
@@ -664,19 +650,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>2011</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>0.0650194764089038</v>
@@ -684,19 +670,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>2011</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>0.0831755295078485</v>
@@ -704,19 +690,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>2011</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>1.70697116366317</v>
@@ -724,19 +710,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>2011</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>0.371679765847419</v>
@@ -744,19 +730,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>2011</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>5.8313213323221</v>
@@ -764,19 +750,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>2011</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
         <v>1.32718406657664</v>
@@ -784,19 +770,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>2011</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>1.43902</v>
@@ -804,19 +790,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>2011</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>-4.34193050866706</v>
@@ -824,19 +810,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>2011</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>0.148518539485187</v>
@@ -844,19 +830,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>2012</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>0.0345120172650878</v>
@@ -864,19 +850,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>2012</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>0.0848339268537185</v>
@@ -884,19 +870,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
         <v>2012</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>1.43885066981546</v>
@@ -904,19 +890,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>2012</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
         <v>0.437181679924391</v>
@@ -924,19 +910,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>2012</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
         <v>5.93049086755427</v>
@@ -944,19 +930,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>2012</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>1.368057320858</v>
@@ -964,19 +950,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>2012</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
         <v>1.74512</v>
@@ -984,19 +970,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>2012</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
         <v>-4.0757488823337</v>
@@ -1004,19 +990,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>2012</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
         <v>0.155720283892911</v>
@@ -1024,19 +1010,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>2013</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
         <v>0.0320276065918464</v>
@@ -1044,19 +1030,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>2013</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
         <v>0.0788068873407593</v>
@@ -1064,19 +1050,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>2013</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>1.44981185370682</v>
@@ -1084,19 +1070,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
         <v>2013</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
         <v>0.384306719387177</v>
@@ -1104,19 +1090,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
         <v>2013</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
         <v>5.92972220805312</v>
@@ -1124,19 +1110,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
         <v>2013</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
         <v>1.35144134383595</v>
@@ -1144,19 +1130,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>2013</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
         <v>0.44036</v>
@@ -1164,19 +1150,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>2013</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
         <v>-4.23564091866705</v>
@@ -1184,19 +1170,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>2013</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
         <v>0.162337653546274</v>
@@ -1204,19 +1190,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>14</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
       </c>
       <c r="D38" t="n">
         <v>2014</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
         <v>0.0366562328160499</v>
@@ -1224,19 +1210,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>2014</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
         <v>0.0748290996781293</v>
@@ -1244,19 +1230,19 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D40" t="n">
         <v>2014</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
         <v>1.98868059985196</v>
@@ -1264,19 +1250,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D41" t="n">
         <v>2014</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
         <v>0.359859158382464</v>
@@ -1284,19 +1270,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
         <v>2014</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
         <v>6.01161406082704</v>
@@ -1304,19 +1290,19 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
         <v>2014</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>1.37809602563512</v>
@@ -1324,19 +1310,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
         <v>2014</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
         <v>1.41689</v>
@@ -1344,19 +1330,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
         <v>2014</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
         <v>-4.0515968863337</v>
@@ -1364,19 +1350,19 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
         <v>2014</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
         <v>0.168175762299596</v>
@@ -1384,19 +1370,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
       </c>
       <c r="D47" t="n">
         <v>2015</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
         <v>0.0385666625689017</v>
@@ -1404,19 +1390,19 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>2015</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
         <v>0.083198195400784</v>
@@ -1424,19 +1410,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
         <v>2015</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
         <v>1.70754338570305</v>
@@ -1444,19 +1430,19 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
         <v>2015</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
         <v>0.422478635952449</v>
@@ -1464,19 +1450,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>2015</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
         <v>6.15379331109561</v>
@@ -1484,19 +1470,19 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>2015</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F52" t="n">
         <v>1.38217072323422</v>
@@ -1504,19 +1490,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" t="n">
         <v>2015</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
         <v>1.12508</v>
@@ -1524,19 +1510,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
         <v>2015</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
         <v>-3.52380569200032</v>
@@ -1544,19 +1530,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
         <v>2015</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
         <v>0.172222859513772</v>
@@ -1564,19 +1550,19 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>14</v>
-      </c>
-      <c r="B56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" t="s">
-        <v>16</v>
       </c>
       <c r="D56" t="n">
         <v>2016</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>0.0365831066694062</v>
@@ -1584,19 +1570,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
         <v>2016</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
         <v>0.0832550148021308</v>
@@ -1604,19 +1590,19 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
         <v>2016</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
         <v>1.70668330078583</v>
@@ -1624,19 +1610,19 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
         <v>2016</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F59" t="n">
         <v>0.350460829633138</v>
@@ -1644,19 +1630,19 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D60" t="n">
         <v>2016</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
         <v>6.38557350947215</v>
@@ -1664,19 +1650,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
         <v>2016</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
         <v>1.36070656381187</v>
@@ -1684,19 +1670,19 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
         <v>2016</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
         <v>1.48084</v>
@@ -1704,19 +1690,19 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
         <v>2016</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
         <v>-3.40929699366698</v>
@@ -1724,19 +1710,19 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D64" t="n">
         <v>2016</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F64" t="n">
         <v>0.177000360217171</v>
@@ -1744,19 +1730,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" t="s">
-        <v>16</v>
       </c>
       <c r="D65" t="n">
         <v>2017</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
         <v>0.0368846017863196</v>
@@ -1764,19 +1750,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D66" t="n">
         <v>2017</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
         <v>0.0949538601445981</v>
@@ -1784,19 +1770,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D67" t="n">
         <v>2017</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
         <v>2.21490182256613</v>
@@ -1804,19 +1790,19 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D68" t="n">
         <v>2017</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
         <v>0.447170045034261</v>
@@ -1824,19 +1810,19 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
         <v>2017</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
         <v>5.75365585517136</v>
@@ -1844,19 +1830,19 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>2017</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
         <v>1.34750904266547</v>
@@ -1864,19 +1850,19 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>2017</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
         <v>1.17049</v>
@@ -1884,19 +1870,19 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72" t="n">
         <v>2017</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
         <v>-4.56110023966708</v>
@@ -1904,19 +1890,19 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>2017</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
         <v>0.180650621428405</v>
@@ -1924,19 +1910,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
         <v>14</v>
-      </c>
-      <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" t="s">
-        <v>16</v>
       </c>
       <c r="D74" t="n">
         <v>2018</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F74" t="n">
         <v>0.033795188211891</v>
@@ -1944,19 +1930,19 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D75" t="n">
         <v>2018</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
         <v>0.0954271151233472</v>
@@ -1964,19 +1950,19 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D76" t="n">
         <v>2018</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F76" t="n">
         <v>1.64077641813119</v>
@@ -1984,19 +1970,19 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
         <v>2018</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
         <v>0.417932127141307</v>
@@ -2004,19 +1990,19 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
         <v>2018</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
         <v>5.6750540218534</v>
@@ -2024,19 +2010,19 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
         <v>2018</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
         <v>1.37036964254227</v>
@@ -2044,19 +2030,19 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D80" t="n">
         <v>2018</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
         <v>1.57046</v>
@@ -2064,19 +2050,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D81" t="n">
         <v>2018</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
         <v>-4.08097359266704</v>
@@ -2084,19 +2070,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D82" t="n">
         <v>2018</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>0.184813412214338</v>
@@ -2104,19 +2090,19 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
         <v>14</v>
-      </c>
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" t="s">
-        <v>16</v>
       </c>
       <c r="D83" t="n">
         <v>2019</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F83" t="n">
         <v>0.0311539374901665</v>
@@ -2124,19 +2110,19 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
         <v>2019</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
         <v>0.0945481681863503</v>
@@ -2144,19 +2130,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D85" t="n">
         <v>2019</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
         <v>1.46336390458282</v>
@@ -2164,19 +2150,19 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D86" t="n">
         <v>2019</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
         <v>0.405475244899604</v>
@@ -2184,19 +2170,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D87" t="n">
         <v>2019</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
         <v>6.47212271377766</v>
@@ -2204,19 +2190,19 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
         <v>2019</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
         <v>1.33926188942195</v>
@@ -2224,19 +2210,19 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D89" t="n">
         <v>2019</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
         <v>1.49188</v>
@@ -2244,19 +2230,19 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D90" t="n">
         <v>2019</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
         <v>-3.40020365666698</v>
@@ -2264,19 +2250,19 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D91" t="n">
         <v>2019</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
         <v>0.192191735849493</v>
@@ -2284,19 +2270,19 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
         <v>14</v>
-      </c>
-      <c r="B92" t="s">
-        <v>15</v>
-      </c>
-      <c r="C92" t="s">
-        <v>16</v>
       </c>
       <c r="D92" t="n">
         <v>2020</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
         <v>0.0351557922267847</v>
@@ -2304,19 +2290,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D93" t="n">
         <v>2020</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
         <v>0.0934257633914284</v>
@@ -2324,19 +2310,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D94" t="n">
         <v>2020</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
         <v>1.50809086825204</v>
@@ -2344,19 +2330,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D95" t="n">
         <v>2020</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
         <v>0.4048563432063</v>
@@ -2364,19 +2350,19 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D96" t="n">
         <v>2020</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
         <v>9.99517041199213</v>
@@ -2384,19 +2370,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D97" t="n">
         <v>2020</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
         <v>1.24441074570654</v>
@@ -2404,19 +2390,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
         <v>2020</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F98" t="n">
         <v>1.63336</v>
@@ -2424,19 +2410,19 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D99" t="n">
         <v>2020</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
         <v>-4.16796168066704</v>
@@ -2444,19 +2430,19 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D100" t="n">
         <v>2020</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F100" t="n">
         <v>0.195164422025213</v>
@@ -2464,19 +2450,19 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
         <v>14</v>
-      </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" t="s">
-        <v>16</v>
       </c>
       <c r="D101" t="n">
         <v>2021</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
         <v>0.0352002145788811</v>
@@ -2484,19 +2470,19 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D102" t="n">
         <v>2021</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F102" t="n">
         <v>0.105946457894715</v>
@@ -2504,19 +2490,19 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D103" t="n">
         <v>2021</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F103" t="n">
         <v>1.60426168054173</v>
@@ -2524,19 +2510,19 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D104" t="n">
         <v>2021</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
         <v>0.420444007272332</v>
@@ -2544,19 +2530,19 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D105" t="n">
         <v>2021</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F105" t="n">
         <v>10.2349567811435</v>
@@ -2564,19 +2550,19 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D106" t="n">
         <v>2021</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F106" t="n">
         <v>1.17088073166172</v>
@@ -2584,19 +2570,19 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>2021</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F107" t="n">
         <v>1.32118</v>
@@ -2604,19 +2590,19 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
         <v>2021</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
         <v>-4.45928599233374</v>
@@ -2624,19 +2610,19 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D109" t="n">
         <v>2021</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
         <v>0.198638177245334</v>
@@ -2644,19 +2630,19 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
         <v>14</v>
-      </c>
-      <c r="B110" t="s">
-        <v>15</v>
-      </c>
-      <c r="C110" t="s">
-        <v>16</v>
       </c>
       <c r="D110" t="n">
         <v>2022</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
         <v>0.0575324744612837</v>
@@ -2664,19 +2650,19 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D111" t="n">
         <v>2022</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F111" t="n">
         <v>0.0803532315369146</v>
@@ -2684,19 +2670,19 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D112" t="n">
         <v>2022</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
         <v>1.10601682377141</v>
@@ -2704,19 +2690,19 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D113" t="n">
         <v>2022</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
         <v>0.668221953680188</v>
@@ -2724,19 +2710,19 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D114" t="n">
         <v>2022</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
         <v>10.0585635222635</v>
@@ -2744,19 +2730,19 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D115" t="n">
         <v>2022</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F115" t="n">
         <v>1.2112503076217</v>
@@ -2764,19 +2750,19 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D116" t="n">
         <v>2022</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F116" t="n">
         <v>0.13056</v>
@@ -2784,19 +2770,19 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D117" t="n">
         <v>2022</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F117" t="n">
         <v>-4.46291742233374</v>
@@ -2804,19 +2790,19 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D118" t="n">
         <v>2022</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
         <v>0.198772067792334</v>

--- a/plots/countries/sectors/Brunei-sectors.xlsx
+++ b/plots/countries/sectors/Brunei-sectors.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2.1) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
